--- a/data/trans_dic/P25A$voluntad-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P25A$voluntad-Estudios-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo para dejar de fumar fue, al menos, por propia voluntad</t>
+          <t>Población cuyo motivo para dejar de fumar fue, al menos, por propia voluntad (tasa de respuesta: 91,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>42,53; 53,87</t>
+          <t>42,86; 53,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>53,17; 63,7</t>
+          <t>53,09; 64,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>44,68; 58,21</t>
+          <t>44,89; 58,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>61,8; 86,5</t>
+          <t>62,56; 86,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>60,42; 81,83</t>
+          <t>58,71; 80,88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46,52; 77,84</t>
+          <t>46,47; 78,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,55; 57,23</t>
+          <t>46,93; 57,09</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>55,84; 65,93</t>
+          <t>55,91; 65,39</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>46,95; 59,32</t>
+          <t>46,78; 58,75</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>57,86; 70,84</t>
+          <t>58,87; 71,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>68,68; 78,27</t>
+          <t>68,47; 78,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>57,66; 69,32</t>
+          <t>57,79; 68,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>54,89; 71,05</t>
+          <t>55,94; 71,4</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>72,38; 83,4</t>
+          <t>72,47; 84,01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>60,37; 73,51</t>
+          <t>60,62; 74,03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>59,83; 69,62</t>
+          <t>59,34; 69,49</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>71,52; 79,13</t>
+          <t>72,31; 79,21</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>60,45; 69,3</t>
+          <t>60,23; 68,93</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>58,33; 78,77</t>
+          <t>57,98; 78,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>66,2; 85,62</t>
+          <t>66,36; 84,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>57,81; 79,0</t>
+          <t>56,87; 79,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>52,19; 76,84</t>
+          <t>49,88; 77,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>69,08; 87,52</t>
+          <t>69,4; 87,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>68,31; 84,92</t>
+          <t>68,18; 84,88</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>58,36; 75,22</t>
+          <t>59,41; 75,19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>70,65; 83,76</t>
+          <t>71,05; 83,86</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>66,55; 80,62</t>
+          <t>65,88; 80,18</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>53,55; 61,28</t>
+          <t>53,56; 61,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>64,17; 70,85</t>
+          <t>63,84; 70,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>55,85; 63,89</t>
+          <t>55,98; 63,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>59,98; 72,58</t>
+          <t>60,04; 72,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>72,9; 81,84</t>
+          <t>72,97; 81,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,97; 74,02</t>
+          <t>64,09; 74,27</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>56,52; 63,28</t>
+          <t>56,57; 63,1</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>67,85; 73,29</t>
+          <t>67,77; 73,22</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>60,3; 66,49</t>
+          <t>60,35; 66,93</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo para dejar de fumar fue, al menos, por propia voluntad</t>
+          <t>Población cuyo motivo para dejar de fumar fue, al menos, por propia voluntad (tasa de respuesta: 91,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>128881; 163256</t>
+          <t>129897; 163402</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>197834; 236991</t>
+          <t>197535; 238601</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>93750; 122135</t>
+          <t>94190; 122147</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29763; 41659</t>
+          <t>30126; 41483</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>41731; 56523</t>
+          <t>40555; 55864</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17505; 29289</t>
+          <t>17488; 29413</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>163495; 201020</t>
+          <t>164834; 200512</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>246343; 290856</t>
+          <t>246636; 288472</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>116171; 146789</t>
+          <t>115761; 145367</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>137176; 167935</t>
+          <t>139548; 170448</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>238831; 272175</t>
+          <t>238108; 272526</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>174170; 209360</t>
+          <t>174536; 206797</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>82999; 107446</t>
+          <t>84590; 107969</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>173781; 200222</t>
+          <t>173987; 201697</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>121392; 147799</t>
+          <t>121881; 148855</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>232295; 270328</t>
+          <t>230407; 269804</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>420405; 465135</t>
+          <t>425068; 465624</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>304150; 348676</t>
+          <t>303038; 346791</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>49248; 66513</t>
+          <t>48955; 66254</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>63724; 82423</t>
+          <t>63881; 81351</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>51803; 70790</t>
+          <t>50966; 70977</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26808; 39464</t>
+          <t>25618; 39577</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>53469; 67745</t>
+          <t>53714; 68090</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>64946; 80735</t>
+          <t>64814; 80691</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>79250; 102148</t>
+          <t>80680; 102110</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>122697; 145471</t>
+          <t>123390; 145637</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>122897; 148888</t>
+          <t>121674; 148071</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>334485; 382759</t>
+          <t>334505; 382484</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>523706; 578177</t>
+          <t>520980; 577329</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>335912; 384293</t>
+          <t>336690; 384581</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>150391; 181985</t>
+          <t>150536; 181390</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>281802; 316349</t>
+          <t>282067; 314939</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>213512; 247041</t>
+          <t>213924; 247900</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>494708; 553869</t>
+          <t>495184; 552332</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>816026; 881413</t>
+          <t>815047; 880525</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>563957; 621868</t>
+          <t>564407; 625936</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P25A$voluntad-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P25A$voluntad-Estudios-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>42,86; 53,92</t>
+          <t>43,19; 54,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>53,09; 64,13</t>
+          <t>53,73; 63,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>44,89; 58,22</t>
+          <t>44,6; 57,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>62,56; 86,14</t>
+          <t>63,13; 85,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>58,71; 80,88</t>
+          <t>60,32; 82,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46,47; 78,16</t>
+          <t>44,72; 76,41</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,93; 57,09</t>
+          <t>46,87; 57,35</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>55,91; 65,39</t>
+          <t>56,05; 65,66</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>46,78; 58,75</t>
+          <t>46,83; 58,89</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>58,87; 71,9</t>
+          <t>58,73; 70,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>68,47; 78,37</t>
+          <t>69,04; 78,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>57,79; 68,47</t>
+          <t>57,64; 68,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55,94; 71,4</t>
+          <t>54,7; 71,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>72,47; 84,01</t>
+          <t>72,44; 83,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>60,62; 74,03</t>
+          <t>60,36; 73,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>59,34; 69,49</t>
+          <t>59,55; 68,8</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>72,31; 79,21</t>
+          <t>71,67; 79,09</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>60,23; 68,93</t>
+          <t>60,3; 69,57</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>57,98; 78,47</t>
+          <t>57,7; 78,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>66,36; 84,51</t>
+          <t>66,49; 84,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>56,87; 79,2</t>
+          <t>56,44; 78,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>49,88; 77,06</t>
+          <t>51,1; 78,09</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>69,4; 87,97</t>
+          <t>69,95; 87,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>68,18; 84,88</t>
+          <t>67,82; 85,48</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>59,41; 75,19</t>
+          <t>58,93; 75,43</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>71,05; 83,86</t>
+          <t>70,54; 83,62</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>65,88; 80,18</t>
+          <t>65,88; 79,68</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>53,56; 61,24</t>
+          <t>53,85; 61,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>63,84; 70,74</t>
+          <t>63,91; 70,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>55,98; 63,94</t>
+          <t>56,31; 64,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>60,04; 72,34</t>
+          <t>60,06; 71,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>72,97; 81,47</t>
+          <t>73,32; 81,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,09; 74,27</t>
+          <t>64,23; 74,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>56,57; 63,1</t>
+          <t>56,47; 63,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>67,77; 73,22</t>
+          <t>67,98; 73,47</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>60,35; 66,93</t>
+          <t>60,23; 66,57</t>
         </is>
       </c>
     </row>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>129897; 163402</t>
+          <t>130894; 164376</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>197535; 238601</t>
+          <t>199902; 235451</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>94190; 122147</t>
+          <t>93579; 121104</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30126; 41483</t>
+          <t>30402; 41379</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>40555; 55864</t>
+          <t>41664; 56699</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17488; 29413</t>
+          <t>16829; 28754</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>164834; 200512</t>
+          <t>164605; 201412</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>246636; 288472</t>
+          <t>247253; 289650</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>115761; 145367</t>
+          <t>115868; 145733</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>139548; 170448</t>
+          <t>139227; 168061</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>238108; 272526</t>
+          <t>240090; 273023</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>174536; 206797</t>
+          <t>174098; 208320</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>84590; 107969</t>
+          <t>82712; 108060</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>173987; 201697</t>
+          <t>173931; 201372</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>121881; 148855</t>
+          <t>121372; 148727</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>230407; 269804</t>
+          <t>231233; 267131</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>425068; 465624</t>
+          <t>421310; 464930</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>303038; 346791</t>
+          <t>303360; 350008</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>48955; 66254</t>
+          <t>48719; 66627</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>63881; 81351</t>
+          <t>64006; 81632</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>50966; 70977</t>
+          <t>50574; 70558</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>25618; 39577</t>
+          <t>26247; 40109</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>53714; 68090</t>
+          <t>54142; 67586</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>64814; 80691</t>
+          <t>64472; 81269</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>80680; 102110</t>
+          <t>80026; 102425</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>123390; 145637</t>
+          <t>122507; 145215</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>121674; 148071</t>
+          <t>121676; 147158</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>334505; 382484</t>
+          <t>336313; 385026</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>520980; 577329</t>
+          <t>521546; 576324</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>336690; 384581</t>
+          <t>338667; 385053</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>150536; 181390</t>
+          <t>150598; 180176</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>282067; 314939</t>
+          <t>283419; 315071</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>213924; 247900</t>
+          <t>214389; 249112</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>495184; 552332</t>
+          <t>494299; 553554</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>815047; 880525</t>
+          <t>817611; 883544</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>564407; 625936</t>
+          <t>563252; 622609</t>
         </is>
       </c>
     </row>
